--- a/public/data/db-source/organization.xlsx
+++ b/public/data/db-source/organization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E015A671-E2D0-C641-BFBE-0A1817B35663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2285D9B2-9665-6145-8999-ACF1CAFF7687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="500" windowWidth="31600" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="524">
   <si>
     <t>id</t>
   </si>
@@ -1124,9 +1124,6 @@
     <t>2007</t>
   </si>
   <si>
-    <t>2010</t>
-  </si>
-  <si>
     <t>1983/09/05</t>
   </si>
   <si>
@@ -1614,6 +1611,12 @@
   </si>
   <si>
     <t>bevnat-info</t>
+  </si>
+  <si>
+    <t>2028/08</t>
+  </si>
+  <si>
+    <t>2029/10</t>
   </si>
 </sst>
 </file>
@@ -2064,7 +2067,7 @@
         <v>357</v>
       </c>
       <c r="I2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2089,11 +2092,11 @@
       <c r="G3" t="s">
         <v>358</v>
       </c>
-      <c r="H3" t="s">
-        <v>359</v>
+      <c r="H3">
+        <v>2030</v>
       </c>
       <c r="I3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2116,13 +2119,13 @@
         <v>224</v>
       </c>
       <c r="G4" t="s">
+        <v>359</v>
+      </c>
+      <c r="H4" t="s">
         <v>360</v>
       </c>
-      <c r="H4" t="s">
-        <v>361</v>
-      </c>
       <c r="I4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2145,13 +2148,13 @@
         <v>226</v>
       </c>
       <c r="G5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H5" t="s">
-        <v>363</v>
+        <v>522</v>
       </c>
       <c r="I5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2174,13 +2177,13 @@
         <v>228</v>
       </c>
       <c r="G6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2203,13 +2206,13 @@
         <v>230</v>
       </c>
       <c r="G7" t="s">
+        <v>364</v>
+      </c>
+      <c r="H7" t="s">
         <v>365</v>
       </c>
-      <c r="H7" t="s">
-        <v>366</v>
-      </c>
       <c r="I7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J7" t="s">
         <v>217</v>
@@ -2235,16 +2238,16 @@
         <v>232</v>
       </c>
       <c r="G8" t="s">
+        <v>366</v>
+      </c>
+      <c r="H8" t="s">
         <v>367</v>
       </c>
-      <c r="H8" t="s">
-        <v>368</v>
-      </c>
       <c r="I8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2267,13 +2270,13 @@
         <v>234</v>
       </c>
       <c r="G9" t="s">
+        <v>368</v>
+      </c>
+      <c r="H9" t="s">
         <v>369</v>
       </c>
-      <c r="H9" t="s">
-        <v>370</v>
-      </c>
       <c r="I9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2296,10 +2299,10 @@
         <v>236</v>
       </c>
       <c r="G10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2322,13 +2325,13 @@
         <v>238</v>
       </c>
       <c r="G11" t="s">
+        <v>371</v>
+      </c>
+      <c r="H11" t="s">
         <v>372</v>
       </c>
-      <c r="H11" t="s">
-        <v>373</v>
-      </c>
       <c r="I11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2351,16 +2354,16 @@
         <v>240</v>
       </c>
       <c r="G12" t="s">
+        <v>373</v>
+      </c>
+      <c r="H12" t="s">
         <v>374</v>
       </c>
-      <c r="H12" t="s">
-        <v>375</v>
-      </c>
       <c r="I12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2383,13 +2386,13 @@
         <v>242</v>
       </c>
       <c r="G13" t="s">
+        <v>375</v>
+      </c>
+      <c r="H13" t="s">
         <v>376</v>
       </c>
-      <c r="H13" t="s">
-        <v>377</v>
-      </c>
       <c r="I13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2412,13 +2415,13 @@
         <v>244</v>
       </c>
       <c r="G14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I14" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J14" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2441,7 +2444,7 @@
         <v>246</v>
       </c>
       <c r="G15" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2464,13 +2467,13 @@
         <v>248</v>
       </c>
       <c r="G16" t="s">
+        <v>379</v>
+      </c>
+      <c r="H16" t="s">
         <v>380</v>
       </c>
-      <c r="H16" t="s">
-        <v>381</v>
-      </c>
       <c r="I16" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2493,10 +2496,10 @@
         <v>250</v>
       </c>
       <c r="G17" t="s">
+        <v>381</v>
+      </c>
+      <c r="H17" t="s">
         <v>382</v>
-      </c>
-      <c r="H17" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2519,16 +2522,16 @@
         <v>252</v>
       </c>
       <c r="G18" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H18" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I18" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J18" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2551,16 +2554,16 @@
         <v>254</v>
       </c>
       <c r="G19" t="s">
+        <v>384</v>
+      </c>
+      <c r="H19" t="s">
         <v>385</v>
       </c>
-      <c r="H19" t="s">
-        <v>386</v>
-      </c>
       <c r="I19" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J19" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2583,10 +2586,10 @@
         <v>256</v>
       </c>
       <c r="G20" t="s">
+        <v>386</v>
+      </c>
+      <c r="H20" t="s">
         <v>387</v>
-      </c>
-      <c r="H20" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2609,10 +2612,10 @@
         <v>258</v>
       </c>
       <c r="G21" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I21" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2635,10 +2638,10 @@
         <v>260</v>
       </c>
       <c r="G22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I22" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J22" t="s">
         <v>217</v>
@@ -2664,13 +2667,13 @@
         <v>262</v>
       </c>
       <c r="G23" t="s">
+        <v>390</v>
+      </c>
+      <c r="H23" t="s">
         <v>391</v>
       </c>
-      <c r="H23" t="s">
-        <v>392</v>
-      </c>
       <c r="I23" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2693,13 +2696,13 @@
         <v>264</v>
       </c>
       <c r="G24" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H24" t="s">
-        <v>375</v>
+        <v>523</v>
       </c>
       <c r="I24" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2722,10 +2725,10 @@
         <v>266</v>
       </c>
       <c r="G25" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2748,10 +2751,10 @@
         <v>268</v>
       </c>
       <c r="G26" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I26" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2774,10 +2777,10 @@
         <v>270</v>
       </c>
       <c r="G27" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I27" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2800,13 +2803,13 @@
         <v>272</v>
       </c>
       <c r="G28" t="s">
+        <v>396</v>
+      </c>
+      <c r="H28" t="s">
         <v>397</v>
       </c>
-      <c r="H28" t="s">
-        <v>398</v>
-      </c>
       <c r="I28" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2829,13 +2832,13 @@
         <v>274</v>
       </c>
       <c r="G29" t="s">
+        <v>398</v>
+      </c>
+      <c r="H29" t="s">
         <v>399</v>
       </c>
-      <c r="H29" t="s">
-        <v>400</v>
-      </c>
       <c r="I29" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2858,10 +2861,10 @@
         <v>276</v>
       </c>
       <c r="G30" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I30" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2884,13 +2887,13 @@
         <v>278</v>
       </c>
       <c r="G31" t="s">
+        <v>400</v>
+      </c>
+      <c r="H31" t="s">
         <v>401</v>
       </c>
-      <c r="H31" t="s">
-        <v>402</v>
-      </c>
       <c r="I31" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2913,10 +2916,10 @@
         <v>280</v>
       </c>
       <c r="H32" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I32" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2939,13 +2942,13 @@
         <v>282</v>
       </c>
       <c r="G33" t="s">
+        <v>403</v>
+      </c>
+      <c r="H33" t="s">
         <v>404</v>
       </c>
-      <c r="H33" t="s">
-        <v>405</v>
-      </c>
       <c r="I33" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2968,13 +2971,13 @@
         <v>284</v>
       </c>
       <c r="G34" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H34" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I34" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2997,7 +3000,7 @@
         <v>286</v>
       </c>
       <c r="I35" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3020,10 +3023,10 @@
         <v>288</v>
       </c>
       <c r="G36" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I36" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3046,13 +3049,13 @@
         <v>290</v>
       </c>
       <c r="G37" t="s">
+        <v>406</v>
+      </c>
+      <c r="H37" t="s">
         <v>407</v>
       </c>
-      <c r="H37" t="s">
-        <v>408</v>
-      </c>
       <c r="J37" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3075,16 +3078,16 @@
         <v>292</v>
       </c>
       <c r="G38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H38" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I38" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J38" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3107,13 +3110,13 @@
         <v>294</v>
       </c>
       <c r="G39" t="s">
+        <v>409</v>
+      </c>
+      <c r="H39" t="s">
         <v>410</v>
       </c>
-      <c r="H39" t="s">
-        <v>411</v>
-      </c>
       <c r="I39" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3136,16 +3139,16 @@
         <v>296</v>
       </c>
       <c r="G40" t="s">
+        <v>411</v>
+      </c>
+      <c r="H40" t="s">
         <v>412</v>
       </c>
-      <c r="H40" t="s">
-        <v>413</v>
-      </c>
       <c r="I40" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J40" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3168,13 +3171,13 @@
         <v>298</v>
       </c>
       <c r="G41" t="s">
+        <v>413</v>
+      </c>
+      <c r="H41" t="s">
         <v>414</v>
       </c>
-      <c r="H41" t="s">
-        <v>415</v>
-      </c>
       <c r="I41" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3197,10 +3200,10 @@
         <v>300</v>
       </c>
       <c r="G42" t="s">
+        <v>415</v>
+      </c>
+      <c r="H42" t="s">
         <v>416</v>
-      </c>
-      <c r="H42" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3223,10 +3226,10 @@
         <v>302</v>
       </c>
       <c r="G43" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I43" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3249,10 +3252,10 @@
         <v>304</v>
       </c>
       <c r="G44" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I44" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3275,10 +3278,10 @@
         <v>306</v>
       </c>
       <c r="G45" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I45" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3301,13 +3304,13 @@
         <v>308</v>
       </c>
       <c r="G46" t="s">
+        <v>418</v>
+      </c>
+      <c r="H46" t="s">
         <v>419</v>
       </c>
-      <c r="H46" t="s">
-        <v>420</v>
-      </c>
       <c r="I46" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3330,10 +3333,10 @@
         <v>310</v>
       </c>
       <c r="G47" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I47" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3356,13 +3359,13 @@
         <v>312</v>
       </c>
       <c r="G48" t="s">
+        <v>421</v>
+      </c>
+      <c r="H48" t="s">
         <v>422</v>
       </c>
-      <c r="H48" t="s">
-        <v>423</v>
-      </c>
       <c r="I48" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3385,13 +3388,13 @@
         <v>314</v>
       </c>
       <c r="G49" t="s">
+        <v>423</v>
+      </c>
+      <c r="H49" t="s">
         <v>424</v>
       </c>
-      <c r="H49" t="s">
-        <v>425</v>
-      </c>
       <c r="I49" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3417,7 +3420,7 @@
         <v>358</v>
       </c>
       <c r="I50" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3440,10 +3443,10 @@
         <v>318</v>
       </c>
       <c r="G51" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I51" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3466,16 +3469,16 @@
         <v>320</v>
       </c>
       <c r="G52" t="s">
+        <v>426</v>
+      </c>
+      <c r="H52" t="s">
         <v>427</v>
       </c>
-      <c r="H52" t="s">
-        <v>428</v>
-      </c>
       <c r="I52" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J52" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3498,16 +3501,16 @@
         <v>322</v>
       </c>
       <c r="G53" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H53" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I53" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J53" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3530,10 +3533,10 @@
         <v>324</v>
       </c>
       <c r="G54" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I54" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3556,10 +3559,10 @@
         <v>326</v>
       </c>
       <c r="G55" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I55" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3582,13 +3585,13 @@
         <v>328</v>
       </c>
       <c r="G56" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H56" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I56" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3611,10 +3614,10 @@
         <v>330</v>
       </c>
       <c r="G57" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I57" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3637,13 +3640,13 @@
         <v>332</v>
       </c>
       <c r="G58" t="s">
+        <v>433</v>
+      </c>
+      <c r="H58" t="s">
         <v>434</v>
       </c>
-      <c r="H58" t="s">
-        <v>435</v>
-      </c>
       <c r="I58" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J58" t="s">
         <v>218</v>
@@ -3669,10 +3672,10 @@
         <v>334</v>
       </c>
       <c r="G59" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I59" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3695,16 +3698,16 @@
         <v>336</v>
       </c>
       <c r="G60" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H60" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I60" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J60" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3727,10 +3730,10 @@
         <v>338</v>
       </c>
       <c r="G61" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I61" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3753,13 +3756,13 @@
         <v>340</v>
       </c>
       <c r="G62" t="s">
+        <v>438</v>
+      </c>
+      <c r="H62" t="s">
         <v>439</v>
       </c>
-      <c r="H62" t="s">
-        <v>440</v>
-      </c>
       <c r="I62" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3782,10 +3785,10 @@
         <v>342</v>
       </c>
       <c r="G63" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I63" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3808,13 +3811,13 @@
         <v>344</v>
       </c>
       <c r="G64" t="s">
+        <v>441</v>
+      </c>
+      <c r="H64" t="s">
         <v>442</v>
       </c>
-      <c r="H64" t="s">
-        <v>443</v>
-      </c>
       <c r="I64" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3837,7 +3840,7 @@
         <v>346</v>
       </c>
       <c r="J65" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3860,13 +3863,13 @@
         <v>348</v>
       </c>
       <c r="G66" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H66" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I66" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3889,13 +3892,13 @@
         <v>350</v>
       </c>
       <c r="G67" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I67" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J67" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3918,13 +3921,13 @@
         <v>352</v>
       </c>
       <c r="G68" t="s">
+        <v>445</v>
+      </c>
+      <c r="H68" t="s">
         <v>446</v>
       </c>
-      <c r="H68" t="s">
-        <v>447</v>
-      </c>
       <c r="I68" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3947,10 +3950,10 @@
         <v>354</v>
       </c>
       <c r="G69" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I69" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3973,10 +3976,10 @@
         <v>356</v>
       </c>
       <c r="H70" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I70" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
